--- a/EKG_Kalite_Yönetim_Sistemi/00_Yönetim Sistemi Çerçevesi/05_Ürün Güvenliği, Mevzuat ve Sorumluluk/EKG-KLT-MTR-01_urun_mevzuati_varis_ulkesi_tip_onayi_ve_uretim_uygunlug.xlsx
+++ b/EKG_Kalite_Yönetim_Sistemi/00_Yönetim Sistemi Çerçevesi/05_Ürün Güvenliği, Mevzuat ve Sorumluluk/EKG-KLT-MTR-01_urun_mevzuati_varis_ulkesi_tip_onayi_ve_uretim_uygunlug.xlsx
@@ -884,7 +884,8 @@
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:headerFooter differentOddEven="0" differentFirst="0" scaleWithDoc="0" alignWithMargins="1">
     <x:oddHeader>&amp;L&amp;"Arial,Bold"&amp;11EKG-KLT-MTR-01&amp;C&amp;"Arial,Regular"&amp;11Ürün Mevzuatı, Varış Ülkesi, Tip Onayı ve Üretim Uygunluğu Gereklilikleri Mat…</x:oddHeader>
-    <x:oddFooter>&amp;L&amp;"Arial,Regular"&amp;11İlk Yayın: 04.05.2026 | Revizyon: 19.10.2026&amp;R&amp;11Sayfa &amp;P / &amp;N</x:oddFooter>
+    <x:oddFooter>&amp;L&amp;"Arial,Regular"&amp;11İlk Yayın: 01.06.2026 | Revizyon: 31.08.2026
+Revizyon nedeni: Doküman kimliği ve ana liste ile tarih eşleşmesi güncellendi.&amp;R&amp;11Sayfa &amp;P / &amp;N</x:oddFooter>
   </x:headerFooter>
   <x:drawing xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R046577f1715142cd"/>
   <x:tableParts count="1">
@@ -1188,7 +1189,8 @@
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:headerFooter differentOddEven="0" differentFirst="0" scaleWithDoc="0" alignWithMargins="1">
     <x:oddHeader>&amp;L&amp;"Arial,Bold"&amp;11EKG-KLT-MTR-01&amp;C&amp;"Arial,Regular"&amp;11Ürün Mevzuatı, Varış Ülkesi, Tip Onayı ve Üretim Uygunluğu Gereklilikleri Mat…</x:oddHeader>
-    <x:oddFooter>&amp;L&amp;"Arial,Regular"&amp;11İlk Yayın: 04.05.2026 | Revizyon: 19.10.2026&amp;R&amp;11Sayfa &amp;P / &amp;N</x:oddFooter>
+    <x:oddFooter>&amp;L&amp;"Arial,Regular"&amp;11İlk Yayın: 01.06.2026 | Revizyon: 31.08.2026
+Revizyon nedeni: Doküman kimliği ve ana liste ile tarih eşleşmesi güncellendi.&amp;R&amp;11Sayfa &amp;P / &amp;N</x:oddFooter>
   </x:headerFooter>
   <x:drawing xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R3897e7ad509a40d8"/>
   <x:tableParts count="1">
@@ -1442,7 +1444,8 @@
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:headerFooter differentOddEven="0" differentFirst="0" scaleWithDoc="0" alignWithMargins="1">
     <x:oddHeader>&amp;L&amp;"Arial,Bold"&amp;11EKG-KLT-MTR-01&amp;C&amp;"Arial,Regular"&amp;11Ürün Mevzuatı, Varış Ülkesi, Tip Onayı ve Üretim Uygunluğu Gereklilikleri Mat…</x:oddHeader>
-    <x:oddFooter>&amp;L&amp;"Arial,Regular"&amp;11İlk Yayın: 04.05.2026 | Revizyon: 19.10.2026&amp;R&amp;11Sayfa &amp;P / &amp;N</x:oddFooter>
+    <x:oddFooter>&amp;L&amp;"Arial,Regular"&amp;11İlk Yayın: 01.06.2026 | Revizyon: 31.08.2026
+Revizyon nedeni: Doküman kimliği ve ana liste ile tarih eşleşmesi güncellendi.&amp;R&amp;11Sayfa &amp;P / &amp;N</x:oddFooter>
   </x:headerFooter>
   <x:drawing xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R0c75a80a8acd458c"/>
   <x:tableParts count="1">
